--- a/education_forms/036_citation_style_quiz--education_forms.xlsx
+++ b/education_forms/036_citation_style_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>title_of_book</t>
+          <t>title_of_book_(italicized)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Title of Book</t>
+          <t>Title of Book (italicized)</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1688,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>title_of_book_(italicized)</t>
+          <t>title_of_book</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Title of Book (italicized)</t>
+          <t>TITLE OF BOOK</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>citation_experience_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>title_of_book</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TITLE OF BOOK</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>some_experience</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Some experience</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>some_experience</t>
+          <t>comfortable</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Some experience</t>
+          <t>Comfortable</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1756,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>comfortable</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Comfortable</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>citation_experience_choices</t>
+          <t>most_challenging_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>apa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>apa</t>
+          <t>mla</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MLA</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mla</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MLA</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>chicago</t>
+          <t>ieee</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>IEEE</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ieee</t>
+          <t>all_equally_challenging</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>All equally challenging</t>
         </is>
       </c>
     </row>
@@ -1858,27 +1858,10 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>all_equally_challenging</t>
+          <t>none_-_i_find_them_all_easy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
-        <is>
-          <t>All equally challenging</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>most_challenging_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>none_-_i_find_them_all_easy</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>None - I find them all easy</t>
         </is>
